--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendra/Git Projects/jitendrakv.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815F81FC-3370-854A-857D-7D71AB7C11B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A82BF7-3E94-5D4A-9E1D-94FD321E570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhD" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="203">
   <si>
     <t>Category</t>
   </si>
@@ -614,6 +614,24 @@
   </si>
   <si>
     <t>Nokia, USA</t>
+  </si>
+  <si>
+    <t>RohitPhD.jpg</t>
+  </si>
+  <si>
+    <t>AmitMTech2026.jpg</t>
+  </si>
+  <si>
+    <t>StutiMTech2027.jpg</t>
+  </si>
+  <si>
+    <t>hanna.jpg</t>
+  </si>
+  <si>
+    <t>IILM University Greater Noida, India</t>
+  </si>
+  <si>
+    <t>Samsung</t>
   </si>
 </sst>
 </file>
@@ -1086,6 +1104,9 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
+      <c r="I6" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1186,6 +1207,9 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
+      <c r="H2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1288,6 +1312,12 @@
       <c r="E8" t="s">
         <v>42</v>
       </c>
+      <c r="F8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1304,6 +1334,9 @@
       </c>
       <c r="E9" t="s">
         <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>202</v>
       </c>
       <c r="J9" t="s">
         <v>45</v>
@@ -2586,6 +2619,9 @@
       <c r="G6" t="s">
         <v>181</v>
       </c>
+      <c r="I6" t="s">
+        <v>200</v>
+      </c>
       <c r="K6" t="s">
         <v>182</v>
       </c>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendra/Git Projects/jitendrakv.github.io/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A82BF7-3E94-5D4A-9E1D-94FD321E570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35E304C-F369-4ACC-B144-B4B89484D4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhD" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="205">
   <si>
     <t>Category</t>
   </si>
@@ -193,15 +193,9 @@
     <t>Manas Das</t>
   </si>
   <si>
-    <t>Data Augmentation \&amp; Latent Space Interpolation</t>
-  </si>
-  <si>
     <t>Senha C. Dange</t>
   </si>
   <si>
-    <t>Kerna Client Operations \&amp; Workflow Governance Platform</t>
-  </si>
-  <si>
     <t>Yashwant Bharti</t>
   </si>
   <si>
@@ -235,21 +229,12 @@
     <t>Praveen Kumar Arya</t>
   </si>
   <si>
-    <t>Sps Erp System</t>
-  </si>
-  <si>
     <t>Vinay Sharma</t>
   </si>
   <si>
-    <t>Job Hr Dashboard</t>
-  </si>
-  <si>
     <t>Saswat Moharana</t>
   </si>
   <si>
-    <t>Job Hive- Job Portal Application</t>
-  </si>
-  <si>
     <t>Vicky Verma</t>
   </si>
   <si>
@@ -632,13 +617,34 @@
   </si>
   <si>
     <t>Samsung</t>
+  </si>
+  <si>
+    <t>SPS ERP System</t>
+  </si>
+  <si>
+    <t>Data Augmentation &amp; Latent Space Interpolation</t>
+  </si>
+  <si>
+    <t>Kerna Client Operations &amp; Workflow Governance Platform</t>
+  </si>
+  <si>
+    <t>Job Hive - Job Portal Application</t>
+  </si>
+  <si>
+    <t>Line of Business (LoB) HR Dashboard</t>
+  </si>
+  <si>
+    <t>Intellect Design Arena Ltd.</t>
+  </si>
+  <si>
+    <t>Medika Bazaar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,6 +656,14 @@
       <sz val="10.5"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -687,11 +701,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -996,26 +1017,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -1024,16 +1045,16 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
@@ -1045,31 +1066,31 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1081,34 +1102,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1120,7 +1141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1143,7 +1164,7 @@
         <v>45864</v>
       </c>
       <c r="H8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1154,51 +1175,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4758E0-2E06-CD49-AFCA-FFAEED49AC86}">
   <dimension ref="A1:J63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="94.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="5"/>
+    <col min="4" max="4" width="111.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
@@ -1208,17 +1235,17 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
@@ -1228,31 +1255,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
@@ -1262,14 +1289,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
@@ -1279,14 +1306,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
@@ -1296,14 +1323,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
@@ -1313,20 +1340,20 @@
         <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D9" t="s">
@@ -1336,20 +1363,20 @@
         <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D10" t="s">
@@ -1362,14 +1389,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D11" t="s">
@@ -1382,14 +1409,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D12" t="s">
@@ -1402,14 +1429,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D13" t="s">
@@ -1422,18 +1449,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -1442,18 +1469,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -1462,18 +1489,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>42</v>
@@ -1482,18 +1509,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>42</v>
@@ -1502,18 +1529,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
         <v>42</v>
@@ -1522,18 +1549,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
         <v>42</v>
@@ -1542,38 +1569,41 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
         <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>204</v>
       </c>
       <c r="J20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E21" t="s">
         <v>42</v>
@@ -1582,38 +1612,41 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
         <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>203</v>
       </c>
       <c r="J22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -1622,18 +1655,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
         <v>42</v>
@@ -1642,35 +1675,35 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
         <v>42</v>
@@ -1679,18 +1712,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="C27" t="s">
-        <v>82</v>
+      <c r="C27" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
         <v>42</v>
@@ -1699,18 +1732,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
-      <c r="C28" t="s">
-        <v>82</v>
+      <c r="C28" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
         <v>42</v>
@@ -1719,18 +1752,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
         <v>82</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
       </c>
       <c r="E29" t="s">
         <v>42</v>
@@ -1739,400 +1772,400 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
         <v>89</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>90</v>
       </c>
-      <c r="D30" t="s">
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
         <v>91</v>
       </c>
-      <c r="E30" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
         <v>93</v>
       </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>94</v>
       </c>
-      <c r="E31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" t="s">
         <v>95</v>
       </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>96</v>
       </c>
-      <c r="E32" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
         <v>97</v>
       </c>
-      <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>98</v>
       </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="J33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" t="s">
         <v>99</v>
       </c>
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" t="s">
+        <v>188</v>
+      </c>
+      <c r="J36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>100</v>
       </c>
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
-      <c r="J34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" t="s">
         <v>101</v>
       </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E37" t="s">
+        <v>42</v>
+      </c>
+      <c r="J37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>102</v>
       </c>
-      <c r="E35" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
         <v>103</v>
       </c>
-      <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E38" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>104</v>
       </c>
-      <c r="E36" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" t="s">
-        <v>193</v>
-      </c>
-      <c r="J36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" t="s">
         <v>105</v>
       </c>
-      <c r="B37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>106</v>
       </c>
-      <c r="E37" t="s">
-        <v>42</v>
-      </c>
-      <c r="J37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" t="s">
         <v>107</v>
       </c>
-      <c r="B38" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>108</v>
       </c>
-      <c r="E38" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B41" t="s">
         <v>109</v>
       </c>
-      <c r="B39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C41" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="D41" t="s">
         <v>111</v>
       </c>
-      <c r="B40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>112</v>
       </c>
-      <c r="E40" t="s">
-        <v>42</v>
-      </c>
-      <c r="J40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" t="s">
         <v>113</v>
       </c>
-      <c r="B41" t="s">
+      <c r="E42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>114</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
         <v>115</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>116</v>
       </c>
-      <c r="E41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
         <v>117</v>
       </c>
-      <c r="B42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>118</v>
       </c>
-      <c r="E42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s">
         <v>119</v>
       </c>
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>120</v>
       </c>
-      <c r="E43" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" t="s">
         <v>121</v>
       </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="E46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>122</v>
       </c>
-      <c r="E44" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" t="s">
         <v>123</v>
       </c>
-      <c r="B45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>124</v>
       </c>
-      <c r="E45" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" t="s">
         <v>125</v>
       </c>
-      <c r="B46" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>126</v>
       </c>
-      <c r="E46" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="B49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" t="s">
         <v>127</v>
       </c>
-      <c r="B47" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>128</v>
       </c>
-      <c r="E47" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" t="s">
         <v>129</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" t="s">
-        <v>115</v>
-      </c>
-      <c r="D49" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" t="s">
-        <v>115</v>
-      </c>
-      <c r="D50" t="s">
-        <v>134</v>
       </c>
       <c r="E50" t="s">
         <v>42</v>
@@ -2141,52 +2174,52 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" t="s">
         <v>135</v>
-      </c>
-      <c r="B51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" t="s">
-        <v>140</v>
       </c>
       <c r="E53" t="s">
         <v>42</v>
@@ -2195,103 +2228,103 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>140</v>
+      </c>
+      <c r="E55" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>141</v>
       </c>
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D56" t="s">
         <v>142</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>143</v>
       </c>
-      <c r="E54" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="B57" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D57" t="s">
         <v>144</v>
       </c>
-      <c r="B55" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" t="s">
-        <v>142</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="E57" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>145</v>
       </c>
-      <c r="E55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="B58" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" t="s">
-        <v>142</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="D58" t="s">
         <v>147</v>
       </c>
-      <c r="E56" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="E58" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>148</v>
       </c>
-      <c r="B57" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" t="s">
-        <v>142</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="B59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" t="s">
         <v>149</v>
-      </c>
-      <c r="E57" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>150</v>
-      </c>
-      <c r="B58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" t="s">
-        <v>151</v>
-      </c>
-      <c r="D58" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" t="s">
-        <v>151</v>
-      </c>
-      <c r="D59" t="s">
-        <v>154</v>
       </c>
       <c r="E59" t="s">
         <v>42</v>
@@ -2300,18 +2333,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
         <v>33</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60" t="s">
         <v>151</v>
-      </c>
-      <c r="D60" t="s">
-        <v>156</v>
       </c>
       <c r="E60" t="s">
         <v>42</v>
@@ -2320,18 +2353,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
         <v>33</v>
       </c>
-      <c r="C61" t="s">
-        <v>151</v>
+      <c r="C61" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D61" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E61" t="s">
         <v>42</v>
@@ -2340,18 +2373,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B62" t="s">
         <v>33</v>
       </c>
-      <c r="C62" t="s">
-        <v>151</v>
+      <c r="C62" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D62" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E62" t="s">
         <v>42</v>
@@ -2360,37 +2393,38 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" t="s">
-        <v>151</v>
+        <v>84</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D63" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
         <v>42</v>
       </c>
       <c r="J63" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0CB0B7-D58C-1941-ACD1-F59BFD833B36}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2407,7 +2441,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G1" t="s">
         <v>7</v>
@@ -2422,35 +2456,35 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -2464,13 +2498,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6960067F-0CCA-7C4D-BA1D-1D24D0A75DDF}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="66.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="66.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2505,15 +2539,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -2525,18 +2559,18 @@
         <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -2548,82 +2582,82 @@
         <v>42</v>
       </c>
       <c r="G3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" t="s">
         <v>173</v>
       </c>
-      <c r="C4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" t="s">
         <v>174</v>
       </c>
-      <c r="E4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>179</v>
-      </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendra/Git Projects/jitendrakv.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A28F07-2E76-4AAD-9375-81F1AB895BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2ABCDB-EF54-0442-918F-AC91FE18B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhD" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="211">
   <si>
     <t>Name</t>
   </si>
@@ -656,6 +656,9 @@
   </si>
   <si>
     <t>NIT Tiruchirappalli, India</t>
+  </si>
+  <si>
+    <t>Synchrony Financial Services</t>
   </si>
 </sst>
 </file>
@@ -1035,22 +1038,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1118,7 +1121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1166,7 +1169,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1181,7 +1184,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1218,22 +1221,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4758E0-2E06-CD49-AFCA-FFAEED49AC86}">
   <dimension ref="A1:K63"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="5"/>
-    <col min="5" max="5" width="111.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="5"/>
+    <col min="5" max="5" width="111.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1268,7 +1271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1351,7 +1354,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1391,7 +1394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1417,7 +1420,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1443,7 +1446,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -1466,7 +1469,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1489,7 +1492,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1558,7 +1561,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -1650,7 +1653,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -1673,7 +1676,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -1722,7 +1725,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -1837,7 +1840,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -1860,7 +1863,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -1883,7 +1886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -1906,7 +1909,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -1929,7 +1932,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -1952,7 +1955,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -1975,7 +1978,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1998,7 +2001,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -2044,7 +2047,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>97</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2096,7 +2099,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -2119,7 +2122,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>103</v>
       </c>
@@ -2142,7 +2145,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>111</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -2231,7 +2234,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -2254,7 +2257,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>117</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>119</v>
       </c>
@@ -2294,7 +2297,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>123</v>
       </c>
@@ -2334,7 +2337,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -2377,7 +2380,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>131</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>133</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -2460,7 +2463,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>138</v>
       </c>
@@ -2479,8 +2482,11 @@
       <c r="F55" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>139</v>
       </c>
@@ -2503,7 +2509,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -2543,7 +2549,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -2566,7 +2572,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -2589,7 +2595,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -2612,7 +2618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>151</v>
       </c>
@@ -2635,7 +2641,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -2668,9 +2674,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0CB0B7-D58C-1941-ACD1-F59BFD833B36}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>156</v>
       </c>
@@ -2725,7 +2731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -2753,13 +2759,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6960067F-0CCA-7C4D-BA1D-1D24D0A75DDF}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="66.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2794,7 +2800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -2817,7 +2823,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>165</v>
       </c>
@@ -2863,7 +2869,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -2886,7 +2892,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>171</v>
       </c>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendra/Git Projects/jitendrakv.github.io/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2ABCDB-EF54-0442-918F-AC91FE18B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FA615B-D267-4B0E-B05C-C391F8B53155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhD" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="214">
   <si>
     <t>Name</t>
   </si>
@@ -659,6 +659,15 @@
   </si>
   <si>
     <t>Synchrony Financial Services</t>
+  </si>
+  <si>
+    <t>JP Morgan</t>
+  </si>
+  <si>
+    <t>Ford</t>
+  </si>
+  <si>
+    <t>Citi Bank</t>
   </si>
 </sst>
 </file>
@@ -1038,22 +1047,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1106,7 +1115,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1121,7 +1130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1136,7 +1145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1151,7 +1160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1178,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1184,7 +1193,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1220,23 +1229,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4758E0-2E06-CD49-AFCA-FFAEED49AC86}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="5"/>
-    <col min="5" max="5" width="111.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="5"/>
+    <col min="5" max="5" width="111.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1294,7 +1304,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1314,7 +1324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1334,7 +1344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1354,7 +1364,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1374,7 +1384,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1394,7 +1404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1420,7 +1430,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1446,7 +1456,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -1469,7 +1479,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1492,7 +1502,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -1515,7 +1525,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1538,7 +1548,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1561,7 +1571,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -1584,7 +1594,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1607,7 +1617,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -1630,7 +1640,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -1653,7 +1663,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -1676,7 +1686,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1702,7 +1712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -1725,7 +1735,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -1751,7 +1761,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1774,7 +1784,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1797,7 +1807,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1817,7 +1827,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -1840,7 +1850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -1863,7 +1873,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -1886,7 +1896,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -1909,7 +1919,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -1928,11 +1938,14 @@
       <c r="F30" t="s">
         <v>41</v>
       </c>
+      <c r="G30" t="s">
+        <v>212</v>
+      </c>
       <c r="K30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -1951,11 +1964,14 @@
       <c r="F31" t="s">
         <v>41</v>
       </c>
+      <c r="G31" t="s">
+        <v>213</v>
+      </c>
       <c r="K31" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -1978,7 +1994,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -2001,7 +2017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -2024,7 +2040,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>95</v>
       </c>
@@ -2047,7 +2063,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>97</v>
       </c>
@@ -2076,7 +2092,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2099,7 +2115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -2122,7 +2138,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>103</v>
       </c>
@@ -2145,7 +2161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -2168,7 +2184,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -2191,7 +2207,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>111</v>
       </c>
@@ -2211,7 +2227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -2234,7 +2250,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -2257,7 +2273,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>117</v>
       </c>
@@ -2277,7 +2293,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>119</v>
       </c>
@@ -2297,7 +2313,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -2317,7 +2333,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>123</v>
       </c>
@@ -2337,7 +2353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -2357,7 +2373,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -2380,7 +2396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -2400,7 +2416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>131</v>
       </c>
@@ -2420,7 +2436,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>133</v>
       </c>
@@ -2443,7 +2459,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -2463,7 +2479,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>138</v>
       </c>
@@ -2486,7 +2502,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>139</v>
       </c>
@@ -2509,7 +2525,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -2528,8 +2544,11 @@
       <c r="F57" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -2549,7 +2568,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -2572,7 +2591,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -2595,7 +2614,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -2618,7 +2637,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>151</v>
       </c>
@@ -2641,7 +2660,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -2665,7 +2684,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K63" xr:uid="{DD4758E0-2E06-CD49-AFCA-FFAEED49AC86}"/>
+  <autoFilter ref="A1:K63" xr:uid="{DD4758E0-2E06-CD49-AFCA-FFAEED49AC86}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="MSc"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2674,9 +2699,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0CB0B7-D58C-1941-ACD1-F59BFD833B36}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2711,7 +2736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>156</v>
       </c>
@@ -2731,7 +2756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -2759,13 +2784,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6960067F-0CCA-7C4D-BA1D-1D24D0A75DDF}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="66.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="66.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2800,7 +2825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -2823,7 +2848,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -2846,7 +2871,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>165</v>
       </c>
@@ -2869,7 +2894,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -2892,7 +2917,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>171</v>
       </c>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FA615B-D267-4B0E-B05C-C391F8B53155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97A7791-9A73-43B9-B20C-26CC61901C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="215">
   <si>
     <t>Name</t>
   </si>
@@ -289,9 +289,6 @@
     <t>partial</t>
   </si>
   <si>
-    <t>Shrestha Bhattacharjee</t>
-  </si>
-  <si>
     <t>NeuralRoute: Graph-Based Traffic Route Optimization for Efficient Urban Mobility</t>
   </si>
   <si>
@@ -668,6 +665,12 @@
   </si>
   <si>
     <t>Citi Bank</t>
+  </si>
+  <si>
+    <t>Shreshtha Bhattacharjee</t>
+  </si>
+  <si>
+    <t>shreshtha.jpg</t>
   </si>
 </sst>
 </file>
@@ -1067,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -1079,16 +1082,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>182</v>
-      </c>
-      <c r="I1" t="s">
-        <v>183</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
@@ -1106,10 +1109,10 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1121,10 +1124,10 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1136,7 +1139,7 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1151,10 +1154,10 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1166,16 +1169,16 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1184,7 +1187,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1201,7 +1204,7 @@
         <v>44068</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1219,7 +1222,7 @@
         <v>45864</v>
       </c>
       <c r="I8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -1266,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>6</v>
@@ -1289,7 +1292,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>27</v>
@@ -1301,7 +1304,7 @@
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -1312,7 +1315,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>27</v>
@@ -1332,13 +1335,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -1352,7 +1355,7 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>27</v>
@@ -1372,7 +1375,7 @@
         <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>27</v>
@@ -1392,7 +1395,7 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>27</v>
@@ -1412,7 +1415,7 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>39</v>
@@ -1424,10 +1427,10 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -1438,7 +1441,7 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>39</v>
@@ -1450,7 +1453,7 @@
         <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
@@ -1464,7 +1467,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>39</v>
@@ -1487,7 +1490,7 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>39</v>
@@ -1510,7 +1513,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>39</v>
@@ -1533,7 +1536,7 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>39</v>
@@ -1556,13 +1559,13 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F14" t="s">
         <v>41</v>
@@ -1579,13 +1582,13 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F15" t="s">
         <v>41</v>
@@ -1602,7 +1605,7 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>39</v>
@@ -1625,7 +1628,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>39</v>
@@ -1648,7 +1651,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>39</v>
@@ -1671,7 +1674,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>39</v>
@@ -1694,7 +1697,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>39</v>
@@ -1706,7 +1709,7 @@
         <v>41</v>
       </c>
       <c r="G20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K20" t="s">
         <v>47</v>
@@ -1720,13 +1723,13 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
@@ -1743,19 +1746,19 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s">
         <v>198</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" t="s">
-        <v>199</v>
       </c>
       <c r="K22" t="s">
         <v>47</v>
@@ -1769,13 +1772,13 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F23" t="s">
         <v>41</v>
@@ -1792,7 +1795,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>39</v>
@@ -1815,7 +1818,7 @@
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>39</v>
@@ -1835,7 +1838,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>39</v>
@@ -1858,7 +1861,7 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>76</v>
@@ -1881,7 +1884,7 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>76</v>
@@ -1904,7 +1907,7 @@
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>76</v>
@@ -1927,7 +1930,7 @@
         <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>84</v>
@@ -1939,7 +1942,7 @@
         <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K30" t="s">
         <v>86</v>
@@ -1947,25 +1950,28 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
         <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
         <v>41</v>
       </c>
       <c r="G31" t="s">
-        <v>213</v>
+        <v>212</v>
+      </c>
+      <c r="I31" t="s">
+        <v>214</v>
       </c>
       <c r="K31" t="s">
         <v>86</v>
@@ -1973,19 +1979,19 @@
     </row>
     <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
         <v>41</v>
@@ -1996,19 +2002,19 @@
     </row>
     <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s">
         <v>41</v>
@@ -2019,19 +2025,19 @@
     </row>
     <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
@@ -2042,19 +2048,19 @@
     </row>
     <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s">
         <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s">
         <v>41</v>
@@ -2065,28 +2071,28 @@
     </row>
     <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
         <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s">
         <v>41</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K36" t="s">
         <v>86</v>
@@ -2094,19 +2100,19 @@
     </row>
     <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
         <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
         <v>41</v>
@@ -2117,19 +2123,19 @@
     </row>
     <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
         <v>41</v>
@@ -2140,19 +2146,19 @@
     </row>
     <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
         <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F39" t="s">
         <v>41</v>
@@ -2163,19 +2169,19 @@
     </row>
     <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
         <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F40" t="s">
         <v>41</v>
@@ -2186,42 +2192,42 @@
     </row>
     <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
         <v>107</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C41" t="s">
-        <v>209</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" t="s">
         <v>109</v>
       </c>
-      <c r="E41" t="s">
-        <v>110</v>
-      </c>
       <c r="F41" t="s">
         <v>41</v>
       </c>
       <c r="G41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D42" s="5">
         <v>2022</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
         <v>41</v>
@@ -2229,65 +2235,65 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
         <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
         <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F44" t="s">
         <v>41</v>
       </c>
       <c r="G44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>208</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" t="s">
         <v>117</v>
-      </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" t="s">
-        <v>209</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" t="s">
-        <v>118</v>
       </c>
       <c r="F45" t="s">
         <v>41</v>
@@ -2295,19 +2301,19 @@
     </row>
     <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" t="s">
         <v>119</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" t="s">
-        <v>209</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" t="s">
-        <v>120</v>
       </c>
       <c r="F46" t="s">
         <v>41</v>
@@ -2315,19 +2321,19 @@
     </row>
     <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>208</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" t="s">
         <v>121</v>
-      </c>
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" t="s">
-        <v>209</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" t="s">
-        <v>122</v>
       </c>
       <c r="F47" t="s">
         <v>41</v>
@@ -2335,19 +2341,19 @@
     </row>
     <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" t="s">
         <v>123</v>
-      </c>
-      <c r="B48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" t="s">
-        <v>209</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" t="s">
-        <v>124</v>
       </c>
       <c r="F48" t="s">
         <v>41</v>
@@ -2355,19 +2361,19 @@
     </row>
     <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>208</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" t="s">
         <v>125</v>
-      </c>
-      <c r="B49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" t="s">
-        <v>209</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" t="s">
-        <v>126</v>
       </c>
       <c r="F49" t="s">
         <v>41</v>
@@ -2375,19 +2381,19 @@
     </row>
     <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>208</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" t="s">
         <v>127</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>209</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E50" t="s">
-        <v>128</v>
       </c>
       <c r="F50" t="s">
         <v>41</v>
@@ -2398,19 +2404,19 @@
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" t="s">
         <v>129</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>209</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E51" t="s">
-        <v>130</v>
       </c>
       <c r="F51" t="s">
         <v>41</v>
@@ -2418,19 +2424,19 @@
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" t="s">
         <v>131</v>
-      </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>209</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E52" t="s">
-        <v>132</v>
       </c>
       <c r="F52" t="s">
         <v>41</v>
@@ -2438,19 +2444,19 @@
     </row>
     <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" t="s">
         <v>133</v>
-      </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" t="s">
-        <v>209</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" t="s">
-        <v>134</v>
       </c>
       <c r="F53" t="s">
         <v>41</v>
@@ -2461,19 +2467,19 @@
     </row>
     <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" t="s">
-        <v>209</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" t="s">
         <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>137</v>
       </c>
       <c r="F54" t="s">
         <v>41</v>
@@ -2481,88 +2487,88 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B55" t="s">
         <v>83</v>
       </c>
       <c r="C55" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E55" t="s">
+        <v>203</v>
+      </c>
+      <c r="F55" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" t="s">
         <v>209</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" t="s">
-        <v>204</v>
-      </c>
-      <c r="F55" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s">
         <v>83</v>
       </c>
       <c r="C56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" t="s">
         <v>41</v>
       </c>
       <c r="K56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" t="s">
         <v>140</v>
       </c>
-      <c r="B57" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" t="s">
-        <v>209</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" t="s">
-        <v>141</v>
-      </c>
       <c r="F57" t="s">
         <v>41</v>
       </c>
       <c r="G57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B58" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" t="s">
-        <v>209</v>
-      </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" t="s">
         <v>143</v>
-      </c>
-      <c r="E58" t="s">
-        <v>144</v>
       </c>
       <c r="F58" t="s">
         <v>41</v>
@@ -2570,19 +2576,19 @@
     </row>
     <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E59" t="s">
         <v>145</v>
-      </c>
-      <c r="B59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" t="s">
-        <v>209</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E59" t="s">
-        <v>146</v>
       </c>
       <c r="F59" t="s">
         <v>41</v>
@@ -2593,19 +2599,19 @@
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E60" t="s">
         <v>147</v>
-      </c>
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E60" t="s">
-        <v>148</v>
       </c>
       <c r="F60" t="s">
         <v>41</v>
@@ -2616,19 +2622,19 @@
     </row>
     <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" t="s">
         <v>149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" t="s">
-        <v>209</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E61" t="s">
-        <v>150</v>
       </c>
       <c r="F61" t="s">
         <v>41</v>
@@ -2639,19 +2645,19 @@
     </row>
     <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>208</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" t="s">
         <v>151</v>
-      </c>
-      <c r="B62" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" t="s">
-        <v>209</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E62" t="s">
-        <v>152</v>
       </c>
       <c r="F62" t="s">
         <v>41</v>
@@ -2662,25 +2668,25 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s">
         <v>83</v>
       </c>
       <c r="C63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" t="s">
+        <v>41</v>
+      </c>
+      <c r="K63" t="s">
         <v>154</v>
-      </c>
-      <c r="F63" t="s">
-        <v>41</v>
-      </c>
-      <c r="K63" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2709,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -2721,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -2738,19 +2744,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
         <v>156</v>
       </c>
-      <c r="B2" t="s">
-        <v>157</v>
-      </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -2758,19 +2764,19 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -2798,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -2827,13 +2833,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -2845,18 +2851,18 @@
         <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -2868,82 +2874,82 @@
         <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" t="s">
         <v>165</v>
       </c>
-      <c r="B4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>166</v>
       </c>
-      <c r="E4" t="s">
-        <v>167</v>
-      </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
         <v>168</v>
       </c>
-      <c r="B5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>169</v>
       </c>
-      <c r="E5" t="s">
-        <v>170</v>
-      </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
         <v>172</v>
       </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K6" t="s">
         <v>173</v>
-      </c>
-      <c r="I6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K6" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97A7791-9A73-43B9-B20C-26CC61901C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB077D6B-0417-4129-ADF0-74B21C4EE106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     <t>Shreshtha Bhattacharjee</t>
   </si>
   <si>
-    <t>shreshtha.jpg</t>
+    <t>shreshtha.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1244,8 +1244,8 @@
     <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB077D6B-0417-4129-ADF0-74B21C4EE106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475377C1-1808-4C54-B688-E10BD2F17788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     <t>Shreshtha Bhattacharjee</t>
   </si>
   <si>
-    <t>shreshtha.jpeg</t>
+    <t>shreshtha.jpg</t>
   </si>
 </sst>
 </file>
